--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_人口推計" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_手帳実績" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_手帳将来推計" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_推計方法" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_村確認事項" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_推計の不確実性" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_推計方法" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_村確認事項" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,9 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="+0;-0"/>
+    <numFmt numFmtId="169" formatCode="+0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -71,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +130,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
@@ -155,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -245,7 +255,55 @@
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -719,7 +777,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>令和9年度末 手帳所持者数（中位推計）</t>
+          <t>令和9年 手帳所持者数（中位推計）</t>
         </is>
       </c>
       <c r="B7" s="5">
@@ -745,7 +803,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>令和10年度末 手帳所持者数（中位推計）</t>
+          <t>令和10年 手帳所持者数（中位推計）</t>
         </is>
       </c>
       <c r="B8" s="12">
@@ -771,7 +829,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>令和11年度末 手帳所持者数（中位推計）</t>
+          <t>令和11年 手帳所持者数（中位推計）</t>
         </is>
       </c>
       <c r="B9" s="5">
@@ -1831,7 +1889,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>性質の異なる2つの方法を併用し、幅を持たせて提示します。方法A・方法Bの差が推計の不確実性の幅です。計画書には単一値ではなく幅を併記してください。すべて数式のため、02_手帳実績への入力で自動更新されます。</t>
+          <t>性質の異なる2つの方法を併用し、幅を持たせて提示します。方法A・方法Bの差が推計の不確実性の幅です。推計の時点は実績と同じ「各年4月1日現在」です（実績が4月1日現在のため、年度末で予測すると1年ずれます）。計画書には単一値ではなく幅を併記してください。不確実性の定量評価は04_推計の不確実性を参照。</t>
         </is>
       </c>
     </row>
@@ -1872,20 +1930,20 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>令和9年度末
-(2027)</t>
+          <t>令和9年
+(2027.4.1)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>令和10年度末
-(2028)</t>
+          <t>令和10年
+(2028.4.1)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>令和11年度末
-(2029)</t>
+          <t>令和11年
+(2029.4.1)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1980,7 +2038,7 @@
       <c r="F9" s="28" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>計画書に記載する場合は中位を代表値とし、A・Bの幅を併記する。</t>
+          <t>前提の異なる2手法の平均であり、それ自体に理論的裏付けはない。計画書ではA〜Bの幅を主に示し、中位は参考値として扱う。</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2123,7 @@
       <c r="F12" s="28" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>計画書に記載する場合は中位を代表値とし、A・Bの幅を併記する。</t>
+          <t>前提の異なる2手法の平均であり、それ自体に理論的裏付けはない。計画書ではA〜Bの幅を主に示し、中位は参考値として扱う。</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2208,7 @@
       <c r="F15" s="28" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>計画書に記載する場合は中位を代表値とし、A・Bの幅を併記する。</t>
+          <t>前提の異なる2手法の平均であり、それ自体に理論的裏付けはない。計画書ではA〜Bの幅を主に示し、中位は参考値として扱う。</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2304,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>令和9年度末</t>
+          <t>令和9年</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>令和10年度末</t>
+          <t>令和10年</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>令和11年度末</t>
+          <t>令和11年</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
@@ -2499,6 +2557,666 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>推計の不確実性（レッドチーム検証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本ブックの推計値をそのまま計画書の確定値として用いてよいかを検証したものです。結論として、現時点の推計は「方向性の目安」であり、令和6〜8年度実績の受領前に確定値として記載することは避けてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1. 方法A（トレンド延長法）の統計的信頼性</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>傾き
+(人/年)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>決定係数
+r²</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>残差
+標準誤差</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>令和9年
+点推計</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>令和9年
+95%予測区間</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>108人</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>76〜141人</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>r²が0.45で、実績の変動の半分以上を直線では説明できない。予測区間が実測値の幅を大きく超える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>5〜17人</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>母数12〜14人に対し傾き−0.3人/年。実質的にノイズであり、10人と11人を区別する意味はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>33人</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>20〜46人</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>増加傾向自体は一貫しているが、予測区間は20〜46人と広く、点推計を目標値の根拠にはできない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>令和11年（目標年度）ではさらに広がり、身体障害者手帳の95%予測区間は63〜144人、精神障害者保健福祉手帳は19〜51人、療育手帳は3〜17人となります。標本が5か年しかなく、そこから3〜6年先を外挿しているためです。点推計（104人・35人・10人）は中心値にすぎず、統計的な確からしさを主張できる数値ではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2. 方法B（所持率法）の分母による感度（令和11年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>総人口
+ベース</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>老年人口
+ベース</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>生産年齢
+人口ベース</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>方法A
+（参考）</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>最大−最小</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>所持者は高齢層に集中するため、総人口ではなく老年人口を分母にすると120人となり、18人増える。仕様書の約130人に近づく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>分母によらず11〜13人。母数が小さく差も小さいが、そもそも推計の意味が薄い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>所持者は生産年齢層が中心とみられ、分母の選択で25〜32人と振れる。方法Aの35人とも乖離する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>本ブックの方法Bは総人口を分母としています。しかし障がい者手帳の所持は年齢構成に強く依存するため、本来は年齢階層別の所持率を用いるべきです。年齢階層別の手帳所持者数は村資料待ちであり、受領後に方法Bを年齢階層別に組み替えることを推奨します（06_村確認事項の該当行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>3. 仕様書の調査対象者数との突合（最重要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>令和5年
+実績</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>仕様書
+（約）</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>本ブックの推計方向</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="D21" s="39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>0.1403508771929824</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>減少（令和11年 102〜104人）</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の数値が令和8年時点の実数であれば、推計の方向と矛盾する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="42" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>横ばい〜減少（10〜11人）</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>仕様書の数値が令和8年時点の実数であれば、推計の方向と矛盾する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D23" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>増加（27〜35人）</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の数値が令和8年時点の実数であれば、推計の方向と矛盾する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="n">
+        <v>156</v>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>190</v>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>34</v>
+      </c>
+      <c r="E24" s="46" t="n">
+        <v>0.217948717948718</v>
+      </c>
+      <c r="F24" s="43" t="inlineStr">
+        <is>
+          <t>減少（145人）</t>
+        </is>
+      </c>
+      <c r="G24" s="43" t="inlineStr">
+        <is>
+          <t>同期間の総人口は約5%減。手帳所持者だけが22%増える説明が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>これは確認事項ではなく、推計を確定できない前提条件です。仕様書の約190人が（a）発送数に余裕を見た概数なのか、（b）集計基準・対象年齢が異なるのか、（c）実際に令和6〜8年で増加しているのか、のいずれであるかによって、推計の方向（減少か増加か）そのものが変わります。村への確認が済むまで、手帳所持者数の将来推計を計画書の確定値として記載しないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>4. 過去稿との数値の異同</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>版</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>方法Bの人口基礎</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+総人口</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>身体</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>療育</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>精神</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>合計（中位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>計画素案 第4〜9稿</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>令和5年から75人/年の定数減（線形）</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>93人</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>10人</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>25人</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="inlineStr">
+        <is>
+          <t>139人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>将来推計ワークブック(20260707)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>こども・子育て計画の公式推計</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D30" s="38" t="inlineStr">
+        <is>
+          <t>102人</t>
+        </is>
+      </c>
+      <c r="E30" s="38" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="F30" s="38" t="inlineStr">
+        <is>
+          <t>27人</t>
+        </is>
+      </c>
+      <c r="G30" s="38" t="inlineStr">
+        <is>
+          <t>145人</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>本ブック</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>こども・子育て計画の公式推計</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>102人</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>11人</t>
+        </is>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>27人</t>
+        </is>
+      </c>
+      <c r="G31" s="34" t="inlineStr">
+        <is>
+          <t>145人</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="62" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>計画素案第4〜9稿の方法Bは、本文では「人口減少率をそのまま延長した簡易推計」と説明していますが、実際の計算は率ではなく定数人数減（平成31年→令和5年の300人減÷4年＝75人/年）です。記載と計算が一致していません。また、第8稿で村公式推計を「第2章2-2の基礎として明記した」と整理していますが、2-2の数値は第7稿から変更されておらず、実際には反映されていません。本ブックは公式推計に統一しているため、第4〜9稿及び前回計画評価表（20260703、身体104→99等）の記載とは一致しません。計画書への転記時は本ブックの値に揃えてください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2630,7 +3348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2708,7 +3426,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2735,7 +3453,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2762,7 +3480,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2781,7 +3499,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>01_人口推計／04_推計方法</t>
+          <t>01_人口推計／05_推計方法</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -2789,7 +3507,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2808,7 +3526,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03_手帳将来推計の留意点</t>
+          <t>03_手帳将来推計／04_推計の不確実性</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -2816,7 +3534,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2843,7 +3561,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -2870,7 +3588,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>

--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_手帳実績" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_手帳将来推計" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_推計の不確実性" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_推計方法" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_村確認事項" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_年齢階級別推計" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_推計方法" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_村確認事項" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -165,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -302,6 +303,12 @@
     </xf>
     <xf numFmtId="169" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2864,7 +2871,7 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>本ブックの方法Bは総人口を分母としています。しかし障がい者手帳の所持は年齢構成に強く依存するため、本来は年齢階層別の所持率を用いるべきです。年齢階層別の手帳所持者数は村資料待ちであり、受領後に方法Bを年齢階層別に組み替えることを推奨します（06_村確認事項の該当行）。</t>
+          <t>本ブックの方法Bは総人口を分母としています。北塩原村は総人口が減る一方で老年人口は増えるため、高齢層に偏る身体障害者手帳では総人口ベースの所持率法が推計を実態と逆方向に働かせます。ただしこれは所持率法そのものの欠陥ではなく、分母の取り方の問題です。年齢階級別の所持率を用いれば所持率法は有効に使えるため、村から年齢階級別の手帳所持者数を受領した時点で05_年齢階級別推計（方法C）へ切り替えます。</t>
         </is>
       </c>
     </row>
@@ -3217,132 +3224,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>推計方法と前提</t>
+          <t>年齢階級別所持率法（方法C・村資料受領後に使用）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画書 第2章及びアンケート調査報告書に転記するための、推計方法の説明です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>方法</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>考え方</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>特性・留意点</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>方法A　トレンド延長法</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>手帳所持者数（実数）の推移を直線回帰し、令和9〜11年度まで延長する。回帰の対象期間は実績が入力されている年数（現在は平成31〜令和5年の5か年）に自動的に追随する。</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>直近の実数の動きをそのまま反映するが、単年の変動に引きずられやすい。北塩原村のように母数が小さい場合、1〜2人の増減が傾きに影響する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>方法B　所持率法</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>基準年（現在は令和5年）の人口に対する手帳所持率が今後も一定と仮定し、村公式の将来人口推計（こども・子育て計画のコーホート変化率法）に乗じる。</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>人口減少の影響を反映するが、所持率自体の変化（精神の増加傾向等）は捉えない。人口推計が村公式値であるため、村の他計画と整合が取りやすい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>中位推計</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>方法Aと方法Bの単純平均。</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>代表値として計画書に記載する場合に用いる。ただし単一値のみを示さず、方法A・方法Bの幅を併記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>人口推計の前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>・令和11年の人口は、北塩原村こども・子育て計画（令和7年3月策定）が示すコーホート変化率法による村公式推計を用いています（総人口2,185人、年少111人、生産年齢1,023人、老年1,051人、高齢化率48.1％）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>・令和7〜10年は、令和6年実績（2,394人）と令和11年公式推計（2,185人）の線形補間です。村独自の人口ビジョンや社人研推計がある場合は、そちらに置き換えて再計算してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>・計画素案第9稿では、平成31〜令和5年の人口減少率をそのまま延長した簡易推計を方法Bに用いていました。本ブックでは村公式推計に統一しています。</t>
+          <t>手帳の所持は年齢構成に強く左右されます。総人口を分母とする方法Bは簡便法であり、年齢階級別人口と年齢階級別所持率が揃った時点で本シートの方法Cへ切り替えてください。算式は「年齢区分別人口 × 年齢区分別手帳所持率」です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1. 身体障害者手帳（5区分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>年齢区分</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+人口</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+所持者数</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>所持率</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+人口</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+推計</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>0〜17歳</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="25">
+        <f>IFERROR(C7/B7,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="19">
+        <f>IFERROR(ROUND(D7*E7,0),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>障がい児支援の対象年齢。就学状況とあわせて確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>18〜39歳</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="25">
+        <f>IFERROR(C8/B8,"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="19">
+        <f>IFERROR(ROUND(D8*E8,0),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>就労・日中活動の中心層</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>40〜64歳</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="25">
+        <f>IFERROR(C9/B9,"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="19">
+        <f>IFERROR(ROUND(D9*E9,0),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>特定疾病により介護保険第2号被保険者となる可能性がある層</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="25">
+        <f>IFERROR(C10/B10,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="19">
+        <f>IFERROR(ROUND(D10*E10,0),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>介護保険優先原則の対象。前期高齢者</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="25">
+        <f>IFERROR(C11/B11,"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="19">
+        <f>IFERROR(ROUND(D11*E11,0),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>後期高齢者。人口が増えるため所持者数も増える可能性が高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>SUM(B7:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>SUM(C7:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="47">
+        <f>IFERROR(C12/B12,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>SUM(E7:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>SUM(F7:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="48" t="inlineStr"/>
+      <c r="H12" s="48" t="inlineStr">
+        <is>
+          <t>方法A・方法B（03_手帳将来推計）と突合する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2. 療育手帳（3区分・コーホート移行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>年齢区分</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+人口</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+所持者数</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>所持率</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+人口</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+推計</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>18歳未満</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="25">
+        <f>IFERROR(C16/B16,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="19">
+        <f>IFERROR(ROUND(D16*E16,0),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>18〜64歳</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="25">
+        <f>IFERROR(C17/B17,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="19">
+        <f>IFERROR(ROUND(D17*E17,0),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="25">
+        <f>IFERROR(C18/B18,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="19">
+        <f>IFERROR(ROUND(D18*E18,0),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>SUM(B16:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>SUM(C16:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="47">
+        <f>IFERROR(C19/B19,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>SUM(E16:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>SUM(F16:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="48" t="inlineStr"/>
+      <c r="H19" s="48" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>18歳未満から18〜64歳、64歳から65歳以上への移動をコーホートとして追跡します。母数が小さいため、推計値は1人単位で丸めてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>3. 精神障害者保健福祉手帳（3区分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>年齢区分</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+人口</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>令和8年
+所持者数</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>所持率</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+人口</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>令和11年
+推計</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>18歳未満</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="25">
+        <f>IFERROR(C24/B24,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="19">
+        <f>IFERROR(ROUND(D24*E24,0),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>18〜64歳</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="25">
+        <f>IFERROR(C25/B25,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="19">
+        <f>IFERROR(ROUND(D25*E25,0),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="25">
+        <f>IFERROR(C26/B26,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="19">
+        <f>IFERROR(ROUND(D26*E26,0),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B27" s="24">
+        <f>SUM(B24:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="24">
+        <f>SUM(C24:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="47">
+        <f>IFERROR(C27/B27,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>SUM(E24:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
+        <f>SUM(F24:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="48" t="inlineStr"/>
+      <c r="H27" s="48" t="inlineStr"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>人口比だけでなく、過去3〜5年の交付数・新規交付・更新・返還・死亡・転出、及び自立支援医療受給者数を併用して補正します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>4. 手帳推計とサービス見込量の関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>・手帳所持者数の推計と、障害福祉サービス見込量の推計は分離します。手帳所持者数が増減しても、サービス利用者数が同じ割合で増減するとは限りません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>・サービス見込量は「北塩原村_サービス見込量.xlsx」の個別積上げによります。手帳推計はサービス見込量の直接の根拠ではなく、計画の基礎データ及び相談支援体制・権利擁護等の施策規模を考える材料として用います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>・北塩原村は母数が小さいため、推計値は1人単位で丸めます。小数点以下の統計値をそのまま計画値にしないでください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3354,7 +3795,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>推計方法と前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>計画書 第2章及びアンケート調査報告書に転記するための、推計方法の説明です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>考え方</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>特性・留意点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>方法A　トレンド延長法</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>手帳所持者数（実数）の推移を直線回帰し、令和9〜11年度まで延長する。回帰の対象期間は実績が入力されている年数（現在は平成31〜令和5年の5か年）に自動的に追随する。</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>直近の実数の動きをそのまま反映するが、単年の変動に引きずられやすい。北塩原村のように母数が小さい場合、1〜2人の増減が傾きに影響する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>方法B　所持率法</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>基準年（現在は令和5年）の人口に対する手帳所持率が今後も一定と仮定し、村公式の将来人口推計（こども・子育て計画のコーホート変化率法）に乗じる。</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>人口減少の影響を反映するが、所持率自体の変化（精神の増加傾向等）は捉えない。人口推計が村公式値であるため、村の他計画と整合が取りやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>中位推計</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>方法Aと方法Bの単純平均。</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>前提の異なる2手法の平均であり、それ自体に理論的裏付けはない。計画書ではA〜Bの幅を主に示し、中位は参考値とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>方法C　年齢階級別所持率法
+（村資料受領後の正式版）</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>年齢区分別人口 × 年齢区分別手帳所持率。身体障害者手帳は0〜17歳／18〜39歳／40〜64歳／65〜74歳／75歳以上の5区分、療育手帳・精神障害者保健福祉手帳は18歳未満／18〜64歳／65歳以上の3区分。</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>年齢構成の変化を織り込めるため、総人口を分母とする方法Bの欠点を解消する。療育手帳はコーホート移行（18歳未満→18〜64歳→65歳以上）を反映する。精神障害者保健福祉手帳は人口比だけでなく交付数・新規交付・更新・返還等の実績を併用する。村から年齢階級別の手帳所持者数を受領した時点で、本方法を正式版とする（05_年齢階級別推計）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>人口推計の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>・令和11年の人口は、北塩原村こども・子育て計画（令和7年3月策定）が示すコーホート変化率法による村公式推計を用いています（総人口2,185人、年少111人、生産年齢1,023人、老年1,051人、高齢化率48.1％）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>・令和7〜10年は、令和6年実績（2,394人）と令和11年公式推計（2,185人）の線形補間です。村独自の人口ビジョンや社人研推計がある場合は、そちらに置き換えて再計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>・計画素案第9稿では、平成31〜令和5年の人口減少率をそのまま延長した簡易推計を方法Bに用いていました。本ブックでは村公式推計に統一しています。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3413,7 +4009,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>身体・療育・精神の各年4月1日現在の所持者数。年齢階層別内訳もあわせて依頼する。</t>
+          <t>身体・療育・精神の各年4月1日現在の所持者数。</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3426,7 +4022,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="47" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3435,25 +4031,25 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>令和2〜4年、令和7〜8年の人口</t>
+          <t>年齢階級別の手帳所持者数</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>総人口・年少人口・生産年齢人口・老年人口（各年4月1日現在）。</t>
+          <t>身体は0〜17歳／18〜39歳／40〜64歳／65〜74歳／75歳以上、療育・精神は18歳未満／18〜64歳／65歳以上の区分。方法C（年齢階級別所持率法）へ切り替えるために必須。</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>01_人口推計</t>
+          <t>05_年齢階級別推計</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E7" s="47" t="inlineStr">
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3462,25 +4058,25 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>調査対象者数と手帳所持者数の差異</t>
+          <t>年齢階級別の人口</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>仕様書の約190人（身体約130・精神約40・療育約20）と、現行計画の156人（令和5年）の差の理由。集計基準・対象年齢・サービス利用者の重複計上の違いを確認する。</t>
+          <t>令和8年及び令和11年の年齢階級別人口。上記と同じ区分。こども・子育て計画の推計に年齢階級別の内訳があればそれを用いる。</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02_手帳実績／アンケート発送設計</t>
+          <t>05_年齢階級別推計</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3489,25 +4085,25 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>村独自の人口ビジョン・将来推計</t>
+          <t>令和2〜4年、令和7〜8年の人口</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>総合振興計画の人口ビジョン、社人研推計等がある場合はその数値。</t>
+          <t>総人口・年少人口・生産年齢人口・老年人口（各年4月1日現在）。</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>01_人口推計／05_推計方法</t>
+          <t>01_人口推計</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E9" s="47" t="inlineStr">
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3516,25 +4112,25 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>身体障害者手帳の減少要因</t>
+          <t>調査対象者数と手帳所持者数の差異</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>老年人口が横ばい〜微減である一方、身体障害者手帳所持者数が減少している要因。手帳更新時期・制度改正・転出入・死亡等の影響を確認する。</t>
+          <t>仕様書の約190人（身体約130・精神約40・療育約20）と、現行計画の156人（令和5年）の差の理由。集計基準・対象年齢・サービス利用者の重複計上の違いを確認する。</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03_手帳将来推計／04_推計の不確実性</t>
+          <t>02_手帳実績／アンケート発送設計</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="inlineStr">
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3543,17 +4139,17 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>精神障害者保健福祉手帳の増加要因</t>
+          <t>村独自の人口ビジョン・将来推計</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>所持者数・所持率とも増加傾向にある背景（受診機会の広がり、相談体制、新規申請の動向等）。</t>
+          <t>総合振興計画の人口ビジョン、社人研推計等がある場合はその数値。</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>03_手帳将来推計／相談支援施策</t>
+          <t>01_人口推計／06_推計方法</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -3561,7 +4157,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E11" s="47" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -3570,25 +4166,79 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>身体障害者手帳の減少要因</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>老年人口が横ばい〜微減である一方、身体障害者手帳所持者数が減少している要因。手帳更新時期・制度改正・転出入・死亡等の影響を確認する。</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>03_手帳将来推計／04_推計の不確実性</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>村資料待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳の増加要因</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>所持者数・所持率とも増加傾向にある背景（受診機会の広がり、相談体制、新規申請の動向等）。</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>03_手帳将来推計／相談支援施策</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>村資料待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>障がい児の就学状況</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>特別支援学校・特別支援学級の在籍者数（令和8年4月1日現在）、卒業予定年度。</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>計画書 第2章／障がい児福祉計画</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E12" s="47" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>

--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -216,9 +216,6 @@
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -229,6 +226,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -302,6 +302,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1084,7 +1087,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編・関連計画より</t>
+          <t>現行計画本編 第2章1</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1105,25 @@
           <t>実績</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
+      <c r="D7" s="17" t="n">
+        <v>2697</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>276</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1437</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>984</v>
+      </c>
       <c r="H7" s="16">
         <f>IFERROR(G7/D7,"")</f>
         <v/>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>村資料待ち</t>
+          <t>現行計画本編 第2章1</t>
         </is>
       </c>
     </row>
@@ -1130,9 +1141,15 @@
           <t>実績</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
+      <c r="D8" s="15" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1369</v>
+      </c>
       <c r="G8" s="15" t="n">
         <v>1006</v>
       </c>
@@ -1142,7 +1159,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>老年人口はこの年（1,006人）をピークに減少に転じている</t>
+          <t>現行計画本編 第2章1。老年人口はこの年（1,006人）をピークに減少に転じている</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1177,25 @@
           <t>実績</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
+      <c r="D9" s="17" t="n">
+        <v>2535</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>231</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>1301</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>1003</v>
+      </c>
       <c r="H9" s="16">
         <f>IFERROR(G9/D9,"")</f>
         <v/>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>村資料待ち</t>
+          <t>現行計画本編 第2章1</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1231,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>現行計画本編より。手帳所持率の基準年</t>
+          <t>現行計画本編 第2章1。手帳所持率の基準年</t>
         </is>
       </c>
     </row>
@@ -1224,16 +1249,16 @@
           <t>実績</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>2394</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <v>180</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="17" t="n">
         <v>1223</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="17" t="n">
         <v>991</v>
       </c>
       <c r="H11" s="16">
@@ -1260,19 +1285,19 @@
           <t>補間推計</t>
         </is>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <f>ROUND($D$11+($D$16-$D$11)*1/5,0)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <f>ROUND($E$11+($E$16-$E$11)*1/5,0)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <f>ROUND($F$11+($F$16-$F$11)*1/5,0)</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <f>ROUND($G$11+($G$16-$G$11)*1/5,0)</f>
         <v/>
       </c>
@@ -1300,19 +1325,19 @@
           <t>補間推計</t>
         </is>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <f>ROUND($D$11+($D$16-$D$11)*2/5,0)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="18">
         <f>ROUND($E$11+($E$16-$E$11)*2/5,0)</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="18">
         <f>ROUND($F$11+($F$16-$F$11)*2/5,0)</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <f>ROUND($G$11+($G$16-$G$11)*2/5,0)</f>
         <v/>
       </c>
@@ -1340,19 +1365,19 @@
           <t>補間推計</t>
         </is>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="18">
         <f>ROUND($D$11+($D$16-$D$11)*3/5,0)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <f>ROUND($E$11+($E$16-$E$11)*3/5,0)</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="18">
         <f>ROUND($F$11+($F$16-$F$11)*3/5,0)</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <f>ROUND($G$11+($G$16-$G$11)*3/5,0)</f>
         <v/>
       </c>
@@ -1380,19 +1405,19 @@
           <t>補間推計</t>
         </is>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="18">
         <f>ROUND($D$11+($D$16-$D$11)*4/5,0)</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="18">
         <f>ROUND($E$11+($E$16-$E$11)*4/5,0)</f>
         <v/>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <f>ROUND($F$11+($F$16-$F$11)*4/5,0)</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <f>ROUND($G$11+($G$16-$G$11)*4/5,0)</f>
         <v/>
       </c>
@@ -1496,33 +1521,33 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>西暦（数式参照用）</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="20" t="n">
         <v>2019</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="20" t="n">
         <v>2020</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="20" t="n">
         <v>2021</v>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="20" t="n">
         <v>2022</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="20" t="n">
         <v>2023</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="20" t="n">
         <v>2025</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="20" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1617,9 +1642,9 @@
       <c r="G6" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>緩やかな減少傾向（高齢化に伴う死亡等の影響を含む）</t>
@@ -1637,24 +1662,24 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>横ばい</t>
@@ -1687,9 +1712,9 @@
       <c r="G8" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>緩やかな増加傾向</t>
@@ -1763,35 +1788,35 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <f>'01_人口推計'!D6</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <f>'01_人口推計'!D7</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <f>'01_人口推計'!D8</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <f>'01_人口推計'!D9</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <f>'01_人口推計'!D10</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <f>'01_人口推計'!D11</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="18">
         <f>'01_人口推計'!D12</f>
         <v/>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="18">
         <f>'01_人口推計'!D13</f>
         <v/>
       </c>
@@ -1914,7 +1939,7 @@
           <t>基準年総人口</t>
         </is>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="18">
         <f>INDEX('01_人口推計'!$D$6:$D$16,MATCH($C$4,'01_人口推計'!$B$6:$B$16,0))</f>
         <v/>
       </c>
@@ -1975,15 +2000,15 @@
           <t>方法A　トレンド延長法</t>
         </is>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2027,OFFSET('02_手帳実績'!$C$6,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6))),0),"")</f>
         <v/>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2028,OFFSET('02_手帳実績'!$C$6,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6))),0),"")</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2029,OFFSET('02_手帳実績'!$C$6,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$6:$J$6))),0),"")</f>
         <v/>
       </c>
@@ -2001,15 +2026,15 @@
           <t>方法B　所持率法</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <f>IFERROR(ROUND($F8*'01_人口推計'!$D$14,0),"")</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <f>IFERROR(ROUND($F8*'01_人口推計'!$D$15,0),"")</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <f>IFERROR(ROUND($F8*'01_人口推計'!$D$16,0),"")</f>
         <v/>
       </c>
@@ -2060,15 +2085,15 @@
           <t>方法A　トレンド延長法</t>
         </is>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2027,OFFSET('02_手帳実績'!$C$7,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7))),0),"")</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2028,OFFSET('02_手帳実績'!$C$7,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7))),0),"")</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2029,OFFSET('02_手帳実績'!$C$7,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$7:$J$7))),0),"")</f>
         <v/>
       </c>
@@ -2086,15 +2111,15 @@
           <t>方法B　所持率法</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <f>IFERROR(ROUND($F11*'01_人口推計'!$D$14,0),"")</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="18">
         <f>IFERROR(ROUND($F11*'01_人口推計'!$D$15,0),"")</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="18">
         <f>IFERROR(ROUND($F11*'01_人口推計'!$D$16,0),"")</f>
         <v/>
       </c>
@@ -2145,15 +2170,15 @@
           <t>方法A　トレンド延長法</t>
         </is>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2027,OFFSET('02_手帳実績'!$C$8,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8))),0),"")</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2028,OFFSET('02_手帳実績'!$C$8,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8))),0),"")</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="18">
         <f>IFERROR(ROUND(FORECAST.LINEAR(2029,OFFSET('02_手帳実績'!$C$8,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8)),OFFSET('02_手帳実績'!$C$4,0,0,1,COUNT('02_手帳実績'!$C$8:$J$8))),0),"")</f>
         <v/>
       </c>
@@ -2171,15 +2196,15 @@
           <t>方法B　所持率法</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <f>IFERROR(ROUND($F14*'01_人口推計'!$D$14,0),"")</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="18">
         <f>IFERROR(ROUND($F14*'01_人口推計'!$D$15,0),"")</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <f>IFERROR(ROUND($F14*'01_人口推計'!$D$16,0),"")</f>
         <v/>
       </c>
@@ -2357,13 +2382,13 @@
           <t>方法B</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="17" t="n">
         <v>106</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="17" t="n">
         <v>104</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="17" t="n">
         <v>102</v>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
@@ -2399,13 +2424,13 @@
           <t>方法A</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="17" t="n">
         <v>10</v>
       </c>
       <c r="F30" s="8" t="inlineStr"/>
@@ -2437,13 +2462,13 @@
           <t>中位</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C32" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="17" t="n">
         <v>11</v>
       </c>
       <c r="F32" s="8" t="inlineStr"/>
@@ -2479,13 +2504,13 @@
           <t>方法B</t>
         </is>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C34" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="17" t="n">
         <v>27</v>
       </c>
       <c r="F34" s="8" t="inlineStr"/>
@@ -2521,13 +2546,13 @@
           <t>中位</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="17" t="n">
         <v>149</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="17" t="n">
         <v>147</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="17" t="n">
         <v>145</v>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
@@ -2564,7 +2589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2820,19 +2845,19 @@
           <t>療育手帳</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2956,10 +2981,10 @@
           <t>療育手帳</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D22" s="41" t="n">
@@ -3047,168 +3072,474 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>4. 過去稿との数値の異同</t>
+          <t>4. 手帳所持率の推移と方法D（所持率トレンド法）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>現行計画本編（令和6年3月）の受領により、平成31年から令和5年までの年齢3区分別人口が判明したため、各年の手帳所持率を算定できるようになりました。方法Bは令和5年の所持率が将来も一定と仮定していますが、実際には所持率が上昇しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>平成31年</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>令和2年</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>令和3年</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>令和4年</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>令和5年</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>傾向</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="n">
+        <v>0.04594</v>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>0.04486</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>0.04867</v>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>横ばい（4.49〜4.87％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="B31" s="47" t="n">
+        <v>0.00474</v>
+      </c>
+      <c r="C31" s="47" t="n">
+        <v>0.00482</v>
+      </c>
+      <c r="D31" s="47" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="E31" s="47" t="n">
+        <v>0.00473</v>
+      </c>
+      <c r="F31" s="47" t="n">
+        <v>0.00491</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>横ばい</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="D32" s="28" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="E32" s="28" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="F32" s="28" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>明確な上昇（平成31年比＋40％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B33" s="47" t="n">
+        <v>0.05942</v>
+      </c>
+      <c r="C33" s="47" t="n">
+        <v>0.06007</v>
+      </c>
+      <c r="D33" s="47" t="n">
+        <v>0.06426</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="F33" s="47" t="n">
+        <v>0.06386</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>上昇（5.94％→6.39％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>方法A
+トレンド延長</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>方法B
+所持率一定</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>方法D
+所持率トレンド</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>中位
+（A・B平均）</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>103</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>実数は減少しているが所持率は横ばい。方法Dは所持率のわずかな上昇を拾って高めに出る</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>療育手帳</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>いずれの方法でも10〜11人。差に意味はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>方法Dが方法Aと一致。方法Bの27人は所持率一定の仮定による過小推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>145</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>方法Dは中位より12人多い</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳では、所持率トレンドを延長した方法Dが35人となり、実数のトレンドを延長した方法Aの35人と一致します。所持率一定を仮定する方法Bの27人は、所持率が上昇している実態を反映できていません。一方で身体障害者手帳は、方法Dが111人と方法A（104人）・方法B（102人）を上回ります。母数が小さく所持率の年次変動が大きいため、方法Dも単独では確定値になりません。村から年齢階級別の手帳所持者数を受領し、05_年齢階級別推計（方法C）へ移行することが本筋です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>5. 過去稿との数値の異同</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>方法Bの人口基礎</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>令和11年
 総人口</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>身体</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>療育</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>精神</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>合計（中位）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>計画素案 第4〜9稿</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>令和5年から75人/年の定数減（線形）</t>
         </is>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C44" s="15" t="n">
         <v>1993</v>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D44" s="34" t="inlineStr">
         <is>
           <t>93人</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E44" s="34" t="inlineStr">
         <is>
           <t>10人</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>25人</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G44" s="34" t="inlineStr">
         <is>
           <t>139人</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>将来推計ワークブック(20260707)</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>こども・子育て計画の公式推計</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C45" s="17" t="n">
         <v>2185</v>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>102人</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>11人</t>
         </is>
       </c>
-      <c r="F30" s="38" t="inlineStr">
+      <c r="F45" s="38" t="inlineStr">
         <is>
           <t>27人</t>
         </is>
       </c>
-      <c r="G30" s="38" t="inlineStr">
+      <c r="G45" s="38" t="inlineStr">
         <is>
           <t>145人</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>本ブック</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>こども・子育て計画の公式推計</t>
         </is>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C46" s="15" t="n">
         <v>2185</v>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D46" s="34" t="inlineStr">
         <is>
           <t>102人</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E46" s="34" t="inlineStr">
         <is>
           <t>11人</t>
         </is>
       </c>
-      <c r="F31" s="34" t="inlineStr">
+      <c r="F46" s="34" t="inlineStr">
         <is>
           <t>27人</t>
         </is>
       </c>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G46" s="34" t="inlineStr">
         <is>
           <t>145人</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="62" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="47" ht="62" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>計画素案第4〜9稿の方法Bは、本文では「人口減少率をそのまま延長した簡易推計」と説明していますが、実際の計算は率ではなく定数人数減（平成31年→令和5年の300人減÷4年＝75人/年）です。記載と計算が一致していません。また、第8稿で村公式推計を「第2章2-2の基礎として明記した」と整理していますが、2-2の数値は第7稿から変更されておらず、実際には反映されていません。本ブックは公式推計に統一しているため、第4〜9稿及び前回計画評価表（20260703、身体104→99等）の記載とは一致しません。計画書への転記時は本ブックの値に揃えてください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A32:G32"/>
+  <mergeCells count="13">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A10:G10"/>
@@ -3306,14 +3637,14 @@
           <t>0〜17歳</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
       <c r="D7" s="25">
         <f>IFERROR(C7/B7,"")</f>
         <v/>
       </c>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="19">
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="18">
         <f>IFERROR(ROUND(D7*E7,0),"")</f>
         <v/>
       </c>
@@ -3330,14 +3661,14 @@
           <t>18〜39歳</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
       <c r="D8" s="25">
         <f>IFERROR(C8/B8,"")</f>
         <v/>
       </c>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="19">
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="18">
         <f>IFERROR(ROUND(D8*E8,0),"")</f>
         <v/>
       </c>
@@ -3354,14 +3685,14 @@
           <t>40〜64歳</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
       <c r="D9" s="25">
         <f>IFERROR(C9/B9,"")</f>
         <v/>
       </c>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="19">
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="18">
         <f>IFERROR(ROUND(D9*E9,0),"")</f>
         <v/>
       </c>
@@ -3378,14 +3709,14 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
       <c r="D10" s="25">
         <f>IFERROR(C10/B10,"")</f>
         <v/>
       </c>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="19">
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="18">
         <f>IFERROR(ROUND(D10*E10,0),"")</f>
         <v/>
       </c>
@@ -3402,14 +3733,14 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
       <c r="D11" s="25">
         <f>IFERROR(C11/B11,"")</f>
         <v/>
       </c>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="19">
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="18">
         <f>IFERROR(ROUND(D11*E11,0),"")</f>
         <v/>
       </c>
@@ -3434,7 +3765,7 @@
         <f>SUM(C7:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="48">
         <f>IFERROR(C12/B12,"")</f>
         <v/>
       </c>
@@ -3446,8 +3777,8 @@
         <f>SUM(F7:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="48" t="inlineStr"/>
-      <c r="H12" s="48" t="inlineStr">
+      <c r="G12" s="49" t="inlineStr"/>
+      <c r="H12" s="49" t="inlineStr">
         <is>
           <t>方法A・方法B（03_手帳将来推計）と突合する</t>
         </is>
@@ -3508,14 +3839,14 @@
           <t>18歳未満</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
       <c r="D16" s="25">
         <f>IFERROR(C16/B16,"")</f>
         <v/>
       </c>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="19">
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="18">
         <f>IFERROR(ROUND(D16*E16,0),"")</f>
         <v/>
       </c>
@@ -3528,14 +3859,14 @@
           <t>18〜64歳</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
       <c r="D17" s="25">
         <f>IFERROR(C17/B17,"")</f>
         <v/>
       </c>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="19">
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="18">
         <f>IFERROR(ROUND(D17*E17,0),"")</f>
         <v/>
       </c>
@@ -3548,14 +3879,14 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
       <c r="D18" s="25">
         <f>IFERROR(C18/B18,"")</f>
         <v/>
       </c>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="19">
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="18">
         <f>IFERROR(ROUND(D18*E18,0),"")</f>
         <v/>
       </c>
@@ -3576,7 +3907,7 @@
         <f>SUM(C16:C18)</f>
         <v/>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="48">
         <f>IFERROR(C19/B19,"")</f>
         <v/>
       </c>
@@ -3588,8 +3919,8 @@
         <f>SUM(F16:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="48" t="inlineStr"/>
-      <c r="H19" s="48" t="inlineStr"/>
+      <c r="G19" s="49" t="inlineStr"/>
+      <c r="H19" s="49" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -3653,14 +3984,14 @@
           <t>18歳未満</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
       <c r="D24" s="25">
         <f>IFERROR(C24/B24,"")</f>
         <v/>
       </c>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="19">
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="18">
         <f>IFERROR(ROUND(D24*E24,0),"")</f>
         <v/>
       </c>
@@ -3673,14 +4004,14 @@
           <t>18〜64歳</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
       <c r="D25" s="25">
         <f>IFERROR(C25/B25,"")</f>
         <v/>
       </c>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="19">
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="18">
         <f>IFERROR(ROUND(D25*E25,0),"")</f>
         <v/>
       </c>
@@ -3693,14 +4024,14 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
       <c r="D26" s="25">
         <f>IFERROR(C26/B26,"")</f>
         <v/>
       </c>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="19">
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="18">
         <f>IFERROR(ROUND(D26*E26,0),"")</f>
         <v/>
       </c>
@@ -3721,7 +4052,7 @@
         <f>SUM(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="48">
         <f>IFERROR(C27/B27,"")</f>
         <v/>
       </c>
@@ -3733,8 +4064,8 @@
         <f>SUM(F24:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="48" t="inlineStr"/>
-      <c r="H27" s="48" t="inlineStr"/>
+      <c r="G27" s="49" t="inlineStr"/>
+      <c r="H27" s="49" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -4022,7 +4353,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="49" t="inlineStr">
+      <c r="E6" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4049,7 +4380,7 @@
           <t>最優先</t>
         </is>
       </c>
-      <c r="E7" s="49" t="inlineStr">
+      <c r="E7" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4076,7 +4407,7 @@
           <t>最優先</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4103,7 +4434,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E9" s="49" t="inlineStr">
+      <c r="E9" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4130,7 +4461,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4157,7 +4488,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E11" s="49" t="inlineStr">
+      <c r="E11" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4184,7 +4515,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E12" s="49" t="inlineStr">
+      <c r="E12" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4211,7 +4542,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr">
+      <c r="E13" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>
@@ -4238,7 +4569,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E14" s="49" t="inlineStr">
+      <c r="E14" s="50" t="inlineStr">
         <is>
           <t>村資料待ち</t>
         </is>

--- a/output/北塩原村_将来推計.xlsx
+++ b/output/北塩原村_将来推計.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_年齢階級別推計" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_推計方法" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_村確認事項" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_県との比較" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="+0.00;-0.00"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="+0;-0"/>
     <numFmt numFmtId="169" formatCode="+0%"/>
+    <numFmt numFmtId="170" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -166,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,6 +317,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4582,4 +4596,268 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>福島県の精神障害者保健福祉手帳所持者数との比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>精神保健福祉資料（630調査）自治体票による福島県の所持者数。本村の精神障害者保健福祉手帳所持者数が5年間で約40%増加していることが県全体の傾向と比べてどうかを確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1. 福島県の所持者数（630調査 自治体票）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>所持者数</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1級</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2級</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3級</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>18002</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>1469</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>9443</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>7090</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>19107</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>9879</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>7829</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>2年間の増減率</t>
+        </is>
+      </c>
+      <c r="B9" s="52">
+        <f>IFERROR(B8/B7-1,"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="52">
+        <f>IFERROR(C8/C7-1,"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="52">
+        <f>IFERROR(D8/D7-1,"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="52">
+        <f>IFERROR(E8/E7-1,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>令和5年度から令和7年度への変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2. 本村との比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>起点</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>直近</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>増減率</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>年平均</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>福島県（精神手帳所持者数）</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>18002</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>19107</v>
+      </c>
+      <c r="D13" s="53">
+        <f>IFERROR(C13/B13-1,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="53">
+        <f>IFERROR((C13/B13)^(1/2)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>令和5年度→令和7年度の2年間</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>本村（精神手帳所持者数）</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="54">
+        <f>IFERROR(C14/B14-1,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>IFERROR((C14/B14)^(1/4)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>平成31年→令和5年の4年間。母数が小さく1人の増減が3〜4%に相当する</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>※ 県・村とも精神障害者保健福祉手帳の所持者数は増加しており、方法B（所持率一定）が精神で成り立たないという本ブック03・04の判断と方向が一致する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>※ 期間が異なる（県は2年、村は4年）ため直接比較はできない。年平均で比較する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>※【検討したが採用しなかった方法】630調査 自治体票には手帳の「交付件数」の性年齢階級別内訳があるが（福島県 令和7年度1,016件）、これは所持者数19,107人の約5%にすぎず、2年更新の制度であることを踏まえると新規交付のみと考えられる。新規交付は40歳以上65歳未満が約48%を占め、所持者全体の年齢構成とは異なる。このため、県の交付件数の年齢構成を本村の所持者に当てはめる方法は採らない。年齢階級別の推計（方法C）には、引き続き村の年齢階級別所持者数が必要である。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>